--- a/ABET/DocumentTracker_Assessment.xlsx
+++ b/ABET/DocumentTracker_Assessment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usarmywestpoint-my.sharepoint.com/personal/andrew_biaglow_westpoint_edu/Documents/Documents/GitHub/abiaglow.github.io/ABET/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A339169-5F03-43D1-B0D1-973AE804511A}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4C24B4C-F800-408D-BCE3-BAF1805A30FF}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{188796DA-674F-42F3-8244-EB71C3832B77}"/>
+    <workbookView xWindow="22932" yWindow="-72" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{188796DA-674F-42F3-8244-EB71C3832B77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="57">
   <si>
     <t>ü</t>
   </si>
@@ -306,7 +306,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -679,11 +679,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -829,26 +840,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
@@ -861,11 +857,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
@@ -911,10 +904,34 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1250,15 +1267,15 @@
     <row r="3" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C3" s="13"/>
       <c r="D3" s="23"/>
-      <c r="E3" s="71" t="s">
+      <c r="E3" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="73"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="102"/>
     </row>
     <row r="4" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C4" s="14"/>
@@ -1284,15 +1301,15 @@
       <c r="K4" s="15">
         <v>2026</v>
       </c>
-      <c r="N4" s="74" t="s">
+      <c r="N4" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="O4" s="75"/>
+      <c r="O4" s="104"/>
       <c r="P4" s="42"/>
-      <c r="R4" s="74" t="s">
+      <c r="R4" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="S4" s="75"/>
+      <c r="S4" s="104"/>
       <c r="T4" s="42"/>
       <c r="V4" s="54" t="s">
         <v>45</v>
@@ -1309,12 +1326,12 @@
       <c r="C5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="76"/>
+      <c r="D5" s="71"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
       <c r="J5" s="58"/>
       <c r="K5" s="17"/>
       <c r="N5" s="41" t="s">
@@ -1358,20 +1375,20 @@
       <c r="C6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="76"/>
+      <c r="D6" s="71"/>
       <c r="E6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F6" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H6" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I6" s="77" t="s">
+      <c r="F6" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I6" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J6" s="52" t="s">
@@ -1421,20 +1438,20 @@
       <c r="C7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="76"/>
+      <c r="D7" s="71"/>
       <c r="E7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F7" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G7" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H7" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I7" s="77" t="s">
+      <c r="F7" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J7" s="52" t="s">
@@ -1484,20 +1501,20 @@
       <c r="C8" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="76"/>
+      <c r="D8" s="71"/>
       <c r="E8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F8" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H8" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I8" s="77" t="s">
+      <c r="F8" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J8" s="52" t="s">
@@ -1560,7 +1577,7 @@
       <c r="H9" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="77" t="s">
+      <c r="I9" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J9" s="63" t="s">
@@ -1671,12 +1688,12 @@
       <c r="C11" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="76"/>
+      <c r="D11" s="71"/>
       <c r="E11" s="50"/>
       <c r="F11" s="51"/>
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
-      <c r="I11" s="76"/>
+      <c r="I11" s="71"/>
       <c r="J11" s="58"/>
       <c r="K11" s="17"/>
       <c r="N11" s="43" t="s">
@@ -1709,20 +1726,20 @@
       <c r="C12" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="76"/>
+      <c r="D12" s="71"/>
       <c r="E12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F12" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H12" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I12" s="77" t="s">
+      <c r="F12" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H12" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I12" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J12" s="52" t="s">
@@ -1754,14 +1771,14 @@
       <c r="C13" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="76"/>
+      <c r="D13" s="71"/>
       <c r="E13" s="33"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I13" s="77" t="s">
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I13" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J13" s="52" t="s">
@@ -1798,7 +1815,7 @@
       <c r="C14" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="76"/>
+      <c r="D14" s="71"/>
       <c r="E14" s="53"/>
       <c r="F14" s="64"/>
       <c r="G14" s="64"/>
@@ -1912,14 +1929,14 @@
       <c r="C16" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="76"/>
+      <c r="D16" s="71"/>
       <c r="E16" s="50"/>
       <c r="F16" s="51"/>
       <c r="G16" s="51"/>
       <c r="H16" s="51"/>
       <c r="I16" s="51"/>
       <c r="J16" s="60"/>
-      <c r="K16" s="79"/>
+      <c r="K16" s="74"/>
       <c r="N16" s="47" t="s">
         <v>38</v>
       </c>
@@ -1961,26 +1978,26 @@
       <c r="C17" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="76"/>
+      <c r="D17" s="71"/>
       <c r="E17" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F17" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G17" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H17" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I17" s="77" t="s">
+      <c r="F17" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G17" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H17" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I17" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J17" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="K17" s="80" t="s">
+      <c r="K17" s="75" t="s">
         <v>55</v>
       </c>
       <c r="V17" s="43" t="s">
@@ -2006,26 +2023,26 @@
       <c r="C18" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="76"/>
+      <c r="D18" s="71"/>
       <c r="E18" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F18" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G18" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H18" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I18" s="77" t="s">
+      <c r="F18" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H18" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I18" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J18" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="K18" s="80" t="s">
+      <c r="K18" s="75" t="s">
         <v>55</v>
       </c>
       <c r="V18" s="47" t="s">
@@ -2051,26 +2068,26 @@
       <c r="C19" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="76"/>
+      <c r="D19" s="71"/>
       <c r="E19" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F19" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G19" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H19" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I19" s="77" t="s">
+      <c r="F19" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H19" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J19" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="K19" s="81" t="s">
+      <c r="K19" s="76" t="s">
         <v>0</v>
       </c>
       <c r="Z19" s="43" t="s">
@@ -2087,26 +2104,26 @@
       <c r="C20" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="76"/>
+      <c r="D20" s="71"/>
       <c r="E20" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F20" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G20" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H20" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I20" s="77" t="s">
+      <c r="F20" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J20" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="K20" s="80" t="s">
+      <c r="K20" s="75" t="s">
         <v>52</v>
       </c>
       <c r="Z20" s="35" t="s">
@@ -2123,26 +2140,26 @@
       <c r="C21" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="76"/>
+      <c r="D21" s="71"/>
       <c r="E21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H21" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I21" s="77" t="s">
+      <c r="F21" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H21" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I21" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J21" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="K21" s="81" t="s">
+      <c r="K21" s="76" t="s">
         <v>0</v>
       </c>
       <c r="Z21" s="49" t="s">
@@ -2159,26 +2176,26 @@
       <c r="C22" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="76"/>
+      <c r="D22" s="71"/>
       <c r="E22" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F22" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G22" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H22" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I22" s="77" t="s">
+      <c r="F22" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G22" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H22" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I22" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J22" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="K22" s="80" t="s">
+      <c r="K22" s="75" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2205,7 +2222,7 @@
       <c r="J23" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="K23" s="82" t="s">
+      <c r="K23" s="77" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2213,12 +2230,12 @@
       <c r="C24" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="83"/>
+      <c r="D24" s="78"/>
       <c r="E24" s="12"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
+      <c r="F24" s="78"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="78"/>
+      <c r="I24" s="78"/>
       <c r="J24" s="65"/>
       <c r="K24" s="21"/>
     </row>
@@ -2226,20 +2243,20 @@
       <c r="C25" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="83"/>
+      <c r="D25" s="78"/>
       <c r="E25" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F25" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="G25" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="H25" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="I25" s="85" t="s">
+      <c r="F25" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H25" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I25" s="79" t="s">
         <v>0</v>
       </c>
       <c r="J25" s="61" t="s">
@@ -2253,20 +2270,20 @@
       <c r="C26" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="83"/>
+      <c r="D26" s="78"/>
       <c r="E26" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="G26" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="H26" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="I26" s="85" t="s">
+      <c r="F26" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H26" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I26" s="79" t="s">
         <v>0</v>
       </c>
       <c r="J26" s="61" t="s">
@@ -2280,20 +2297,20 @@
       <c r="C27" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="83"/>
+      <c r="D27" s="78"/>
       <c r="E27" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F27" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="G27" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="H27" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="I27" s="85" t="s">
+      <c r="F27" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="79" t="s">
         <v>0</v>
       </c>
       <c r="J27" s="61" t="s">
@@ -2307,20 +2324,20 @@
       <c r="C28" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="83"/>
+      <c r="D28" s="78"/>
       <c r="E28" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F28" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="G28" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="H28" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="I28" s="85" t="s">
+      <c r="F28" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H28" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I28" s="79" t="s">
         <v>0</v>
       </c>
       <c r="J28" s="61" t="s">
@@ -2371,7 +2388,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1630D0AC-2110-454D-A79F-6A4AFC573624}">
-  <dimension ref="C2:AB30"/>
+  <dimension ref="C2:K30"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.796875" customWidth="1"/>
@@ -2381,21 +2398,21 @@
     <col min="12" max="12" width="2.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C3" s="13"/>
       <c r="D3" s="23"/>
-      <c r="E3" s="71" t="s">
+      <c r="E3" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="73"/>
-    </row>
-    <row r="4" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="102"/>
+    </row>
+    <row r="4" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C4" s="14"/>
       <c r="D4" s="11"/>
       <c r="E4" s="10">
@@ -2419,94 +2436,38 @@
       <c r="K4" s="15">
         <v>2026</v>
       </c>
-      <c r="N4" s="74" t="s">
-        <v>48</v>
-      </c>
-      <c r="O4" s="75"/>
-      <c r="P4" s="42"/>
-      <c r="R4" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="S4" s="75"/>
-      <c r="T4" s="42"/>
-      <c r="V4" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" s="55"/>
-      <c r="X4" s="42"/>
-      <c r="Z4" s="54" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA4" s="55"/>
-      <c r="AB4" s="42"/>
-    </row>
-    <row r="5" spans="3:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="76"/>
+      <c r="D5" s="105"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
       <c r="J5" s="58"/>
       <c r="K5" s="17"/>
-      <c r="N5" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="O5" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="R5" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="S5" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="T5" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="V5" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="W5" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="X5" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z5" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA5" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB5" s="34" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="3:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="76"/>
+      <c r="D6" s="105"/>
       <c r="E6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F6" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H6" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I6" s="77" t="s">
+      <c r="F6" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I6" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J6" s="52" t="s">
@@ -2515,61 +2476,25 @@
       <c r="K6" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="N6" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="O6" s="44" t="s">
-        <v>42</v>
-      </c>
-      <c r="P6" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="R6" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="S6" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="T6" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="V6" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="W6" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="X6" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA6" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB6" s="46" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="76"/>
+      <c r="D7" s="105"/>
       <c r="E7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F7" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G7" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H7" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I7" s="77" t="s">
+      <c r="F7" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J7" s="52" t="s">
@@ -2578,61 +2503,25 @@
       <c r="K7" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="N7" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="O7" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="P7" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="R7" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="S7" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="T7" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="V7" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="W7" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="X7" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA7" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB7" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="3:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C8" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="76"/>
+      <c r="D8" s="105"/>
       <c r="E8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F8" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H8" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I8" s="77" t="s">
+      <c r="F8" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J8" s="52" t="s">
@@ -2641,44 +2530,8 @@
       <c r="K8" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="N8" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="O8" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="P8" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="R8" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="S8" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="T8" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="V8" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="W8" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="X8" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA8" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB8" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="3:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C9" s="25" t="s">
         <v>10</v>
       </c>
@@ -2695,7 +2548,7 @@
       <c r="H9" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="77" t="s">
+      <c r="I9" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J9" s="63" t="s">
@@ -2704,44 +2557,8 @@
       <c r="K9" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="N9" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="O9" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="P9" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="R9" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="S9" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="T9" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="V9" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="W9" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="X9" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA9" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB9" s="46" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C10" s="18" t="s">
         <v>3</v>
       </c>
@@ -2765,45 +2582,9 @@
         <v>0</v>
       </c>
       <c r="K10" s="19"/>
-      <c r="N10" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="O10" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="P10" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="R10" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="S10" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="T10" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="V10" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="W10" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="X10" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA10" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB10" s="46" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="C11" s="105" t="s">
+    </row>
+    <row r="11" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C11" s="107" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="60"/>
@@ -2811,53 +2592,28 @@
       <c r="F11" s="51"/>
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
-      <c r="I11" s="76"/>
+      <c r="I11" s="105"/>
       <c r="J11" s="58"/>
       <c r="K11" s="17"/>
-      <c r="N11" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="O11" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="P11" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="R11" s="37"/>
-      <c r="S11" s="37"/>
-      <c r="T11" s="40"/>
-      <c r="U11" s="31"/>
-      <c r="V11" s="37"/>
-      <c r="W11" s="37"/>
-      <c r="X11" s="40"/>
-      <c r="Z11" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA11" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB11" s="46" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="C12" s="106" t="s">
+    </row>
+    <row r="12" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C12" s="24" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="58"/>
       <c r="E12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F12" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H12" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I12" s="77" t="s">
+      <c r="F12" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="H12" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I12" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J12" s="52" t="s">
@@ -2866,37 +2622,19 @@
       <c r="K12" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="40"/>
-      <c r="R12" s="37"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="40"/>
-      <c r="V12" s="37"/>
-      <c r="W12" s="37"/>
-      <c r="X12" s="40"/>
-      <c r="Z12" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA12" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB12" s="46" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="C13" s="106" t="s">
+    </row>
+    <row r="13" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C13" s="24" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="58"/>
       <c r="E13" s="33"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I13" s="77" t="s">
+      <c r="F13" s="108"/>
+      <c r="G13" s="108"/>
+      <c r="H13" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I13" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J13" s="52" t="s">
@@ -2905,35 +2643,12 @@
       <c r="K13" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="N13" s="40"/>
-      <c r="P13" s="40"/>
-      <c r="R13" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="S13" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="T13" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="V13" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="W13" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="X13" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="37"/>
-      <c r="AA13" s="37"/>
-      <c r="AB13" s="40"/>
-    </row>
-    <row r="14" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="C14" s="107" t="s">
+    </row>
+    <row r="14" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C14" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="108"/>
+      <c r="D14" s="99"/>
       <c r="E14" s="53"/>
       <c r="F14" s="64"/>
       <c r="G14" s="64"/>
@@ -2946,462 +2661,297 @@
       <c r="J14" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="K14" s="66" t="s">
-        <v>51</v>
-      </c>
-      <c r="N14" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="O14" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="P14" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="R14" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="S14" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="T14" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="V14" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="W14" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="X14" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="37"/>
-      <c r="AA14" s="37"/>
-      <c r="AB14" s="40"/>
-    </row>
-    <row r="15" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="K14" s="77" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C15" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="83"/>
-      <c r="E15" s="86"/>
-      <c r="F15" s="87"/>
-      <c r="G15" s="87"/>
-      <c r="H15" s="87"/>
-      <c r="I15" s="87"/>
-      <c r="J15" s="88"/>
-      <c r="K15" s="89"/>
-      <c r="N15" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="O15" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="P15" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="R15" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="S15" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="T15" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="V15" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="W15" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="X15" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA15" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB15" s="46" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="D15" s="109"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="82"/>
+      <c r="K15" s="83"/>
+    </row>
+    <row r="16" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C16" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="83"/>
+      <c r="D16" s="109"/>
       <c r="E16" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F16" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="G16" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="H16" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="I16" s="84" t="s">
+      <c r="F16" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="H16" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="I16" s="110" t="s">
         <v>0</v>
       </c>
       <c r="J16" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="K16" s="90" t="s">
+      <c r="K16" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="N16" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="O16" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="P16" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="R16" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="S16" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="T16" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="V16" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="W16" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="X16" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA16" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB16" s="46" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C17" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="83"/>
+      <c r="D17" s="109"/>
       <c r="E17" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F17" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="G17" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="H17" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="I17" s="84" t="s">
+      <c r="F17" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="G17" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="H17" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="I17" s="110" t="s">
         <v>0</v>
       </c>
       <c r="J17" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="K17" s="90" t="s">
+      <c r="K17" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="V17" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="W17" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="X17" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA17" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB17" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C18" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="83"/>
+      <c r="D18" s="109"/>
       <c r="E18" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F18" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="G18" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="H18" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="I18" s="84" t="s">
+      <c r="F18" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="H18" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="I18" s="110" t="s">
         <v>0</v>
       </c>
       <c r="J18" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="K18" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="V18" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="W18" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="X18" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA18" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB18" s="46" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="K18" s="85" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C19" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="83"/>
+      <c r="D19" s="109"/>
       <c r="E19" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F19" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="G19" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="H19" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="I19" s="84" t="s">
+      <c r="F19" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="H19" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="110" t="s">
         <v>0</v>
       </c>
       <c r="J19" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="K19" s="90" t="s">
+      <c r="K19" s="84" t="s">
         <v>52</v>
       </c>
-      <c r="Z19" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA19" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB19" s="46" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C20" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="83"/>
+      <c r="D20" s="109"/>
       <c r="E20" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="G20" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="H20" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="I20" s="84" t="s">
+      <c r="F20" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="110" t="s">
         <v>0</v>
       </c>
       <c r="J20" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="K20" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA20" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB20" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="K20" s="85" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C21" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="83"/>
+      <c r="D21" s="109"/>
       <c r="E21" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F21" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="H21" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="I21" s="84" t="s">
+      <c r="F21" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="H21" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="I21" s="110" t="s">
         <v>0</v>
       </c>
       <c r="J21" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="K21" s="90" t="s">
+      <c r="K21" s="84" t="s">
         <v>52</v>
       </c>
-      <c r="Z21" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA21" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB21" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C22" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="83"/>
+      <c r="D22" s="109"/>
       <c r="E22" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F22" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="G22" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="H22" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="I22" s="84" t="s">
+      <c r="F22" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="G22" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="H22" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="I22" s="110" t="s">
         <v>0</v>
       </c>
       <c r="J22" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="K22" s="92" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="K22" s="86" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C23" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D23" s="83"/>
+      <c r="D23" s="109"/>
       <c r="E23" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F23" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="G23" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="H23" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="I23" s="84" t="s">
+      <c r="F23" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="G23" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="H23" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="I23" s="110" t="s">
         <v>0</v>
       </c>
       <c r="J23" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="K23" s="92" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="C24" s="93" t="s">
+      <c r="K23" s="86" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C24" s="87" t="s">
         <v>50</v>
       </c>
       <c r="D24" s="11"/>
-      <c r="E24" s="94" t="s">
-        <v>0</v>
-      </c>
-      <c r="F24" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="G24" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="H24" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="I24" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="J24" s="96" t="s">
-        <v>0</v>
-      </c>
-      <c r="K24" s="97" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="E24" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="F24" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="G24" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="H24" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="I24" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="J24" s="90" t="s">
+        <v>0</v>
+      </c>
+      <c r="K24" s="91" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C25" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="76"/>
+      <c r="D25" s="105"/>
       <c r="E25" s="1"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
-      <c r="I25" s="76"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="105"/>
       <c r="J25" s="58"/>
       <c r="K25" s="17"/>
     </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C26" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="76"/>
+      <c r="D26" s="105"/>
       <c r="E26" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F26" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G26" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H26" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I26" s="77" t="s">
+      <c r="F26" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="H26" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I26" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J26" s="52" t="s">
@@ -3411,24 +2961,24 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C27" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="76"/>
-      <c r="E27" s="98" t="s">
+      <c r="D27" s="105"/>
+      <c r="E27" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="F27" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G27" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H27" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I27" s="77" t="s">
+      <c r="F27" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J27" s="52" t="s">
@@ -3438,24 +2988,24 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C28" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D28" s="76"/>
+      <c r="D28" s="105"/>
       <c r="E28" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F28" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G28" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H28" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I28" s="77" t="s">
+      <c r="F28" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="H28" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I28" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J28" s="52" t="s">
@@ -3465,24 +3015,24 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C29" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="76"/>
+      <c r="D29" s="105"/>
       <c r="E29" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F29" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G29" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H29" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I29" s="77" t="s">
+      <c r="F29" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G29" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="H29" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J29" s="52" t="s">
@@ -3492,38 +3042,36 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="3:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C30" s="99" t="s">
+    <row r="30" spans="3:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C30" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="100"/>
-      <c r="E30" s="101" t="s">
+      <c r="D30" s="94"/>
+      <c r="E30" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="G30" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="H30" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="I30" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="J30" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="K30" s="104" t="s">
+      <c r="F30" s="96" t="s">
+        <v>0</v>
+      </c>
+      <c r="G30" s="96" t="s">
+        <v>0</v>
+      </c>
+      <c r="H30" s="96" t="s">
+        <v>0</v>
+      </c>
+      <c r="I30" s="96" t="s">
+        <v>0</v>
+      </c>
+      <c r="J30" s="97" t="s">
+        <v>0</v>
+      </c>
+      <c r="K30" s="98" t="s">
         <v>51</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="1">
     <mergeCell ref="E3:K3"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="R4:S4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/ABET/DocumentTracker_Assessment.xlsx
+++ b/ABET/DocumentTracker_Assessment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usarmywestpoint-my.sharepoint.com/personal/andrew_biaglow_westpoint_edu/Documents/Documents/GitHub/abiaglow.github.io/ABET/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4C24B4C-F800-408D-BCE3-BAF1805A30FF}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9D051DB-9FF3-4D20-A655-00DD64EDB79A}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-72" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{188796DA-674F-42F3-8244-EB71C3832B77}"/>
   </bookViews>
@@ -2782,8 +2782,8 @@
       <c r="J19" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="K19" s="84" t="s">
-        <v>52</v>
+      <c r="K19" s="85" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="3:11" x14ac:dyDescent="0.3">

--- a/ABET/DocumentTracker_Assessment.xlsx
+++ b/ABET/DocumentTracker_Assessment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usarmywestpoint-my.sharepoint.com/personal/andrew_biaglow_westpoint_edu/Documents/Documents/GitHub/abiaglow.github.io/ABET/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9D051DB-9FF3-4D20-A655-00DD64EDB79A}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93C23BDC-17CB-4B92-9E02-545E16F81A4C}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-72" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{188796DA-674F-42F3-8244-EB71C3832B77}"/>
+    <workbookView xWindow="28680" yWindow="-4800" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{188796DA-674F-42F3-8244-EB71C3832B77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="57">
   <si>
     <t>ü</t>
   </si>
@@ -694,7 +694,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -905,6 +905,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -919,18 +920,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1267,15 +1256,15 @@
     <row r="3" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C3" s="13"/>
       <c r="D3" s="23"/>
-      <c r="E3" s="100" t="s">
+      <c r="E3" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="102"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="103"/>
     </row>
     <row r="4" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C4" s="14"/>
@@ -1301,15 +1290,15 @@
       <c r="K4" s="15">
         <v>2026</v>
       </c>
-      <c r="N4" s="103" t="s">
+      <c r="N4" s="104" t="s">
         <v>48</v>
       </c>
-      <c r="O4" s="104"/>
+      <c r="O4" s="105"/>
       <c r="P4" s="42"/>
-      <c r="R4" s="103" t="s">
+      <c r="R4" s="104" t="s">
         <v>39</v>
       </c>
-      <c r="S4" s="104"/>
+      <c r="S4" s="105"/>
       <c r="T4" s="42"/>
       <c r="V4" s="54" t="s">
         <v>45</v>
@@ -2388,7 +2377,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1630D0AC-2110-454D-A79F-6A4AFC573624}">
-  <dimension ref="C2:K30"/>
+  <dimension ref="C2:K29"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.796875" customWidth="1"/>
@@ -2402,15 +2391,15 @@
     <row r="3" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C3" s="13"/>
       <c r="D3" s="23"/>
-      <c r="E3" s="100" t="s">
+      <c r="E3" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="102"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="103"/>
     </row>
     <row r="4" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C4" s="14"/>
@@ -2441,12 +2430,12 @@
       <c r="C5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="105"/>
+      <c r="D5" s="71"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="105"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
       <c r="J5" s="58"/>
       <c r="K5" s="17"/>
     </row>
@@ -2454,20 +2443,20 @@
       <c r="C6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="105"/>
+      <c r="D6" s="71"/>
       <c r="E6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F6" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="H6" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I6" s="106" t="s">
+      <c r="F6" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I6" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J6" s="52" t="s">
@@ -2481,20 +2470,20 @@
       <c r="C7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="105"/>
+      <c r="D7" s="71"/>
       <c r="E7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F7" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G7" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="H7" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I7" s="106" t="s">
+      <c r="F7" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J7" s="52" t="s">
@@ -2508,20 +2497,20 @@
       <c r="C8" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="105"/>
+      <c r="D8" s="71"/>
       <c r="E8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F8" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="H8" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I8" s="106" t="s">
+      <c r="F8" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J8" s="52" t="s">
@@ -2548,7 +2537,7 @@
       <c r="H9" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="106" t="s">
+      <c r="I9" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J9" s="63" t="s">
@@ -2584,7 +2573,7 @@
       <c r="K10" s="19"/>
     </row>
     <row r="11" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C11" s="107" t="s">
+      <c r="C11" s="100" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="60"/>
@@ -2592,7 +2581,7 @@
       <c r="F11" s="51"/>
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
-      <c r="I11" s="105"/>
+      <c r="I11" s="71"/>
       <c r="J11" s="58"/>
       <c r="K11" s="17"/>
     </row>
@@ -2604,16 +2593,16 @@
       <c r="E12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F12" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="H12" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I12" s="106" t="s">
+      <c r="F12" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H12" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I12" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J12" s="52" t="s">
@@ -2629,12 +2618,12 @@
       </c>
       <c r="D13" s="58"/>
       <c r="E13" s="33"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I13" s="106" t="s">
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I13" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J13" s="52" t="s">
@@ -2669,7 +2658,7 @@
       <c r="C15" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="109"/>
+      <c r="D15" s="78"/>
       <c r="E15" s="80"/>
       <c r="F15" s="81"/>
       <c r="G15" s="81"/>
@@ -2682,20 +2671,20 @@
       <c r="C16" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="109"/>
+      <c r="D16" s="78"/>
       <c r="E16" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F16" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="G16" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="H16" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="I16" s="110" t="s">
+      <c r="F16" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H16" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I16" s="31" t="s">
         <v>0</v>
       </c>
       <c r="J16" s="61" t="s">
@@ -2709,20 +2698,20 @@
       <c r="C17" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="109"/>
+      <c r="D17" s="78"/>
       <c r="E17" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F17" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="G17" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="H17" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="I17" s="110" t="s">
+      <c r="F17" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H17" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I17" s="31" t="s">
         <v>0</v>
       </c>
       <c r="J17" s="61" t="s">
@@ -2736,20 +2725,20 @@
       <c r="C18" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="109"/>
+      <c r="D18" s="78"/>
       <c r="E18" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F18" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="G18" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="H18" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="I18" s="110" t="s">
+      <c r="F18" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H18" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I18" s="31" t="s">
         <v>0</v>
       </c>
       <c r="J18" s="61" t="s">
@@ -2763,20 +2752,20 @@
       <c r="C19" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="109"/>
+      <c r="D19" s="78"/>
       <c r="E19" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F19" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="G19" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="H19" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="I19" s="110" t="s">
+      <c r="F19" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H19" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="31" t="s">
         <v>0</v>
       </c>
       <c r="J19" s="61" t="s">
@@ -2790,20 +2779,20 @@
       <c r="C20" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="109"/>
+      <c r="D20" s="78"/>
       <c r="E20" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="G20" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="H20" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="I20" s="110" t="s">
+      <c r="F20" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="31" t="s">
         <v>0</v>
       </c>
       <c r="J20" s="61" t="s">
@@ -2817,20 +2806,20 @@
       <c r="C21" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="109"/>
+      <c r="D21" s="78"/>
       <c r="E21" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F21" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="H21" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="I21" s="110" t="s">
+      <c r="F21" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H21" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I21" s="31" t="s">
         <v>0</v>
       </c>
       <c r="J21" s="61" t="s">
@@ -2842,170 +2831,170 @@
     </row>
     <row r="22" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C22" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="78"/>
+      <c r="E22" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="F22" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G22" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H22" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I22" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="J22" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="K22" s="86" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C23" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="109"/>
-      <c r="E22" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="F22" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="G22" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="H22" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="I22" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="J22" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="K22" s="86" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C23" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="109"/>
-      <c r="E23" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="F23" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="G23" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="H23" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="I23" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="J23" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="K23" s="86" t="s">
+      <c r="D23" s="11"/>
+      <c r="E23" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="F23" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="G23" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="H23" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="I23" s="89" t="s">
+        <v>0</v>
+      </c>
+      <c r="J23" s="90" t="s">
+        <v>0</v>
+      </c>
+      <c r="K23" s="91" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C24" s="87" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="F24" s="89" t="s">
-        <v>0</v>
-      </c>
-      <c r="G24" s="89" t="s">
-        <v>0</v>
-      </c>
-      <c r="H24" s="89" t="s">
-        <v>0</v>
-      </c>
-      <c r="I24" s="89" t="s">
-        <v>0</v>
-      </c>
-      <c r="J24" s="90" t="s">
-        <v>0</v>
-      </c>
-      <c r="K24" s="91" t="s">
-        <v>0</v>
-      </c>
+      <c r="C24" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="71"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="17"/>
     </row>
     <row r="25" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C25" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="105"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="105"/>
-      <c r="G25" s="105"/>
-      <c r="H25" s="105"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="17"/>
+      <c r="C25" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="71"/>
+      <c r="E25" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F25" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H25" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I25" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="J25" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="K25" s="70" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C26" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" s="105"/>
-      <c r="E26" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F26" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G26" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="H26" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I26" s="106" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="71"/>
+      <c r="E26" s="92" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H26" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I26" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J26" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="K26" s="66" t="s">
-        <v>51</v>
+      <c r="K26" s="70" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C27" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" s="105"/>
-      <c r="E27" s="92" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G27" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="H27" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I27" s="106" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="71"/>
+      <c r="E27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F27" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J27" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="K27" s="66" t="s">
-        <v>51</v>
+      <c r="K27" s="70" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C28" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="105"/>
+        <v>20</v>
+      </c>
+      <c r="D28" s="71"/>
       <c r="E28" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F28" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G28" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="H28" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I28" s="106" t="s">
+      <c r="F28" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H28" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I28" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J28" s="52" t="s">
@@ -3015,57 +3004,30 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C29" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="105"/>
-      <c r="E29" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F29" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G29" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="H29" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I29" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="J29" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="K29" s="66" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="3:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C30" s="93" t="s">
+    <row r="29" spans="3:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C29" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="94"/>
-      <c r="E30" s="95" t="s">
+      <c r="D29" s="94"/>
+      <c r="E29" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="96" t="s">
-        <v>0</v>
-      </c>
-      <c r="G30" s="96" t="s">
-        <v>0</v>
-      </c>
-      <c r="H30" s="96" t="s">
-        <v>0</v>
-      </c>
-      <c r="I30" s="96" t="s">
-        <v>0</v>
-      </c>
-      <c r="J30" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="K30" s="98" t="s">
+      <c r="F29" s="96" t="s">
+        <v>0</v>
+      </c>
+      <c r="G29" s="96" t="s">
+        <v>0</v>
+      </c>
+      <c r="H29" s="96" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" s="96" t="s">
+        <v>0</v>
+      </c>
+      <c r="J29" s="97" t="s">
+        <v>0</v>
+      </c>
+      <c r="K29" s="98" t="s">
         <v>51</v>
       </c>
     </row>

--- a/ABET/DocumentTracker_Assessment.xlsx
+++ b/ABET/DocumentTracker_Assessment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usarmywestpoint-my.sharepoint.com/personal/andrew_biaglow_westpoint_edu/Documents/Documents/GitHub/abiaglow.github.io/ABET/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93C23BDC-17CB-4B92-9E02-545E16F81A4C}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEC0C664-57D6-48FC-A688-E7CA1ECC4110}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4800" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{188796DA-674F-42F3-8244-EB71C3832B77}"/>
+    <workbookView xWindow="22932" yWindow="-72" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{188796DA-674F-42F3-8244-EB71C3832B77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2608,8 +2608,8 @@
       <c r="J12" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="K12" s="66" t="s">
-        <v>52</v>
+      <c r="K12" s="70" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="3:11" x14ac:dyDescent="0.3">

--- a/ABET/DocumentTracker_Assessment.xlsx
+++ b/ABET/DocumentTracker_Assessment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usarmywestpoint-my.sharepoint.com/personal/andrew_biaglow_westpoint_edu/Documents/Documents/GitHub/abiaglow.github.io/ABET/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEC0C664-57D6-48FC-A688-E7CA1ECC4110}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{669B0ABB-F5C5-4D89-8BAD-770C6E021B67}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-72" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{188796DA-674F-42F3-8244-EB71C3832B77}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="57">
   <si>
     <t>ü</t>
   </si>
@@ -2570,7 +2570,9 @@
       <c r="J10" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="K10" s="19"/>
+      <c r="K10" s="91" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C11" s="100" t="s">

--- a/ABET/DocumentTracker_Assessment.xlsx
+++ b/ABET/DocumentTracker_Assessment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usarmywestpoint-my.sharepoint.com/personal/andrew_biaglow_westpoint_edu/Documents/Documents/GitHub/abiaglow.github.io/ABET/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{669B0ABB-F5C5-4D89-8BAD-770C6E021B67}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{510FBF87-923A-42C9-BE16-FB452038A73B}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-72" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{188796DA-674F-42F3-8244-EB71C3832B77}"/>
   </bookViews>
@@ -3002,8 +3002,8 @@
       <c r="J28" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="K28" s="66" t="s">
-        <v>51</v>
+      <c r="K28" s="70" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="3:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">

--- a/ABET/DocumentTracker_Assessment.xlsx
+++ b/ABET/DocumentTracker_Assessment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usarmywestpoint-my.sharepoint.com/personal/andrew_biaglow_westpoint_edu/Documents/Documents/GitHub/abiaglow.github.io/ABET/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{510FBF87-923A-42C9-BE16-FB452038A73B}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A341C86-E72B-4701-8C4E-954FA9B09F0C}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-72" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{188796DA-674F-42F3-8244-EB71C3832B77}"/>
   </bookViews>
@@ -694,7 +694,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -901,9 +901,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -920,6 +917,20 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1256,15 +1267,15 @@
     <row r="3" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C3" s="13"/>
       <c r="D3" s="23"/>
-      <c r="E3" s="101" t="s">
+      <c r="E3" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="101"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="103"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="102"/>
     </row>
     <row r="4" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C4" s="14"/>
@@ -1290,15 +1301,15 @@
       <c r="K4" s="15">
         <v>2026</v>
       </c>
-      <c r="N4" s="104" t="s">
+      <c r="N4" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="O4" s="105"/>
+      <c r="O4" s="104"/>
       <c r="P4" s="42"/>
-      <c r="R4" s="104" t="s">
+      <c r="R4" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="S4" s="105"/>
+      <c r="S4" s="104"/>
       <c r="T4" s="42"/>
       <c r="V4" s="54" t="s">
         <v>45</v>
@@ -2391,15 +2402,15 @@
     <row r="3" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C3" s="13"/>
       <c r="D3" s="23"/>
-      <c r="E3" s="101" t="s">
+      <c r="E3" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="101"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="103"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="102"/>
     </row>
     <row r="4" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C4" s="14"/>
@@ -2430,12 +2441,12 @@
       <c r="C5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="71"/>
+      <c r="D5" s="105"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
       <c r="J5" s="58"/>
       <c r="K5" s="17"/>
     </row>
@@ -2443,20 +2454,20 @@
       <c r="C6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="71"/>
+      <c r="D6" s="105"/>
       <c r="E6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F6" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="H6" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="I6" s="72" t="s">
+      <c r="F6" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I6" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J6" s="52" t="s">
@@ -2470,20 +2481,20 @@
       <c r="C7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="71"/>
+      <c r="D7" s="105"/>
       <c r="E7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F7" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="G7" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="H7" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="I7" s="72" t="s">
+      <c r="F7" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J7" s="52" t="s">
@@ -2497,20 +2508,20 @@
       <c r="C8" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="71"/>
+      <c r="D8" s="105"/>
       <c r="E8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F8" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="H8" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="I8" s="72" t="s">
+      <c r="F8" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J8" s="52" t="s">
@@ -2537,7 +2548,7 @@
       <c r="H9" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="72" t="s">
+      <c r="I9" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J9" s="63" t="s">
@@ -2575,7 +2586,7 @@
       </c>
     </row>
     <row r="11" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C11" s="100" t="s">
+      <c r="C11" s="99" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="60"/>
@@ -2583,7 +2594,7 @@
       <c r="F11" s="51"/>
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
-      <c r="I11" s="71"/>
+      <c r="I11" s="105"/>
       <c r="J11" s="58"/>
       <c r="K11" s="17"/>
     </row>
@@ -2595,16 +2606,16 @@
       <c r="E12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F12" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="H12" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="I12" s="72" t="s">
+      <c r="F12" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="H12" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I12" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J12" s="52" t="s">
@@ -2620,12 +2631,12 @@
       </c>
       <c r="D13" s="58"/>
       <c r="E13" s="33"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="I13" s="72" t="s">
+      <c r="F13" s="107"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I13" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J13" s="52" t="s">
@@ -2639,7 +2650,7 @@
       <c r="C14" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="99"/>
+      <c r="D14" s="98"/>
       <c r="E14" s="53"/>
       <c r="F14" s="64"/>
       <c r="G14" s="64"/>
@@ -2660,7 +2671,7 @@
       <c r="C15" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="78"/>
+      <c r="D15" s="108"/>
       <c r="E15" s="80"/>
       <c r="F15" s="81"/>
       <c r="G15" s="81"/>
@@ -2673,20 +2684,20 @@
       <c r="C16" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="78"/>
+      <c r="D16" s="108"/>
       <c r="E16" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F16" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="G16" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H16" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="I16" s="31" t="s">
+      <c r="F16" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="H16" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="I16" s="109" t="s">
         <v>0</v>
       </c>
       <c r="J16" s="61" t="s">
@@ -2700,20 +2711,20 @@
       <c r="C17" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="78"/>
+      <c r="D17" s="108"/>
       <c r="E17" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F17" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="G17" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H17" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="I17" s="31" t="s">
+      <c r="F17" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="G17" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="H17" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="I17" s="109" t="s">
         <v>0</v>
       </c>
       <c r="J17" s="61" t="s">
@@ -2727,20 +2738,20 @@
       <c r="C18" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="78"/>
+      <c r="D18" s="108"/>
       <c r="E18" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F18" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="G18" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H18" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="I18" s="31" t="s">
+      <c r="F18" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="H18" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="I18" s="109" t="s">
         <v>0</v>
       </c>
       <c r="J18" s="61" t="s">
@@ -2754,20 +2765,20 @@
       <c r="C19" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="78"/>
+      <c r="D19" s="108"/>
       <c r="E19" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F19" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="G19" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H19" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="I19" s="31" t="s">
+      <c r="F19" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="H19" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="109" t="s">
         <v>0</v>
       </c>
       <c r="J19" s="61" t="s">
@@ -2781,20 +2792,20 @@
       <c r="C20" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="78"/>
+      <c r="D20" s="108"/>
       <c r="E20" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="G20" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H20" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="I20" s="31" t="s">
+      <c r="F20" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="109" t="s">
         <v>0</v>
       </c>
       <c r="J20" s="61" t="s">
@@ -2808,20 +2819,20 @@
       <c r="C21" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="78"/>
+      <c r="D21" s="108"/>
       <c r="E21" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F21" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H21" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="I21" s="31" t="s">
+      <c r="F21" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="H21" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="I21" s="109" t="s">
         <v>0</v>
       </c>
       <c r="J21" s="61" t="s">
@@ -2835,20 +2846,20 @@
       <c r="C22" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="78"/>
+      <c r="D22" s="108"/>
       <c r="E22" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F22" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="G22" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H22" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="I22" s="31" t="s">
+      <c r="F22" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="G22" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="H22" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="I22" s="109" t="s">
         <v>0</v>
       </c>
       <c r="J22" s="61" t="s">
@@ -2889,12 +2900,12 @@
       <c r="C24" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="71"/>
+      <c r="D24" s="105"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="71"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="105"/>
+      <c r="H24" s="105"/>
+      <c r="I24" s="105"/>
       <c r="J24" s="58"/>
       <c r="K24" s="17"/>
     </row>
@@ -2902,20 +2913,20 @@
       <c r="C25" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="71"/>
+      <c r="D25" s="105"/>
       <c r="E25" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F25" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="G25" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="H25" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="I25" s="72" t="s">
+      <c r="F25" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="H25" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I25" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J25" s="52" t="s">
@@ -2929,20 +2940,20 @@
       <c r="C26" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="71"/>
+      <c r="D26" s="105"/>
       <c r="E26" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="G26" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="H26" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="I26" s="72" t="s">
+      <c r="F26" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="H26" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I26" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J26" s="52" t="s">
@@ -2956,20 +2967,20 @@
       <c r="C27" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="71"/>
+      <c r="D27" s="105"/>
       <c r="E27" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F27" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="G27" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="H27" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="I27" s="72" t="s">
+      <c r="F27" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J27" s="52" t="s">
@@ -2983,20 +2994,20 @@
       <c r="C28" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="71"/>
+      <c r="D28" s="105"/>
       <c r="E28" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F28" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="G28" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="H28" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="I28" s="72" t="s">
+      <c r="F28" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="H28" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="I28" s="106" t="s">
         <v>0</v>
       </c>
       <c r="J28" s="52" t="s">
@@ -3029,8 +3040,8 @@
       <c r="J29" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="K29" s="98" t="s">
-        <v>51</v>
+      <c r="K29" s="110" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ABET/DocumentTracker_Assessment.xlsx
+++ b/ABET/DocumentTracker_Assessment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usarmywestpoint-my.sharepoint.com/personal/andrew_biaglow_westpoint_edu/Documents/Documents/GitHub/abiaglow.github.io/ABET/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A341C86-E72B-4701-8C4E-954FA9B09F0C}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16C30DEA-8C95-41EC-BD1F-75F6FB2F9DCC}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-72" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{188796DA-674F-42F3-8244-EB71C3832B77}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{188796DA-674F-42F3-8244-EB71C3832B77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -694,7 +694,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -903,6 +903,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -917,20 +920,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1267,15 +1256,15 @@
     <row r="3" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C3" s="13"/>
       <c r="D3" s="23"/>
-      <c r="E3" s="100" t="s">
+      <c r="E3" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="102"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="103"/>
     </row>
     <row r="4" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C4" s="14"/>
@@ -1301,15 +1290,15 @@
       <c r="K4" s="15">
         <v>2026</v>
       </c>
-      <c r="N4" s="103" t="s">
+      <c r="N4" s="104" t="s">
         <v>48</v>
       </c>
-      <c r="O4" s="104"/>
+      <c r="O4" s="105"/>
       <c r="P4" s="42"/>
-      <c r="R4" s="103" t="s">
+      <c r="R4" s="104" t="s">
         <v>39</v>
       </c>
-      <c r="S4" s="104"/>
+      <c r="S4" s="105"/>
       <c r="T4" s="42"/>
       <c r="V4" s="54" t="s">
         <v>45</v>
@@ -2402,15 +2391,15 @@
     <row r="3" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C3" s="13"/>
       <c r="D3" s="23"/>
-      <c r="E3" s="100" t="s">
+      <c r="E3" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="102"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="103"/>
     </row>
     <row r="4" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C4" s="14"/>
@@ -2441,12 +2430,12 @@
       <c r="C5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="105"/>
+      <c r="D5" s="71"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="105"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
       <c r="J5" s="58"/>
       <c r="K5" s="17"/>
     </row>
@@ -2454,20 +2443,20 @@
       <c r="C6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="105"/>
+      <c r="D6" s="71"/>
       <c r="E6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F6" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="H6" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I6" s="106" t="s">
+      <c r="F6" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I6" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J6" s="52" t="s">
@@ -2481,20 +2470,20 @@
       <c r="C7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="105"/>
+      <c r="D7" s="71"/>
       <c r="E7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F7" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G7" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="H7" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I7" s="106" t="s">
+      <c r="F7" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J7" s="52" t="s">
@@ -2508,27 +2497,27 @@
       <c r="C8" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="105"/>
+      <c r="D8" s="71"/>
       <c r="E8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F8" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="H8" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I8" s="106" t="s">
+      <c r="F8" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J8" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="K8" s="66" t="s">
-        <v>52</v>
+      <c r="K8" s="70" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="3:11" x14ac:dyDescent="0.3">
@@ -2548,7 +2537,7 @@
       <c r="H9" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="106" t="s">
+      <c r="I9" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J9" s="63" t="s">
@@ -2594,7 +2583,7 @@
       <c r="F11" s="51"/>
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
-      <c r="I11" s="105"/>
+      <c r="I11" s="71"/>
       <c r="J11" s="58"/>
       <c r="K11" s="17"/>
     </row>
@@ -2606,16 +2595,16 @@
       <c r="E12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F12" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="H12" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I12" s="106" t="s">
+      <c r="F12" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H12" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I12" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J12" s="52" t="s">
@@ -2631,12 +2620,12 @@
       </c>
       <c r="D13" s="58"/>
       <c r="E13" s="33"/>
-      <c r="F13" s="107"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I13" s="106" t="s">
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I13" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J13" s="52" t="s">
@@ -2671,7 +2660,7 @@
       <c r="C15" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="108"/>
+      <c r="D15" s="78"/>
       <c r="E15" s="80"/>
       <c r="F15" s="81"/>
       <c r="G15" s="81"/>
@@ -2684,20 +2673,20 @@
       <c r="C16" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="108"/>
+      <c r="D16" s="78"/>
       <c r="E16" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F16" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="G16" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="H16" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="I16" s="109" t="s">
+      <c r="F16" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H16" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I16" s="31" t="s">
         <v>0</v>
       </c>
       <c r="J16" s="61" t="s">
@@ -2711,20 +2700,20 @@
       <c r="C17" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="108"/>
+      <c r="D17" s="78"/>
       <c r="E17" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F17" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="G17" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="H17" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="I17" s="109" t="s">
+      <c r="F17" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H17" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I17" s="31" t="s">
         <v>0</v>
       </c>
       <c r="J17" s="61" t="s">
@@ -2738,20 +2727,20 @@
       <c r="C18" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="108"/>
+      <c r="D18" s="78"/>
       <c r="E18" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F18" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="G18" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="H18" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="I18" s="109" t="s">
+      <c r="F18" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H18" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I18" s="31" t="s">
         <v>0</v>
       </c>
       <c r="J18" s="61" t="s">
@@ -2765,20 +2754,20 @@
       <c r="C19" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="108"/>
+      <c r="D19" s="78"/>
       <c r="E19" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F19" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="G19" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="H19" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="I19" s="109" t="s">
+      <c r="F19" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H19" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="31" t="s">
         <v>0</v>
       </c>
       <c r="J19" s="61" t="s">
@@ -2792,20 +2781,20 @@
       <c r="C20" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="108"/>
+      <c r="D20" s="78"/>
       <c r="E20" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="G20" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="H20" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="I20" s="109" t="s">
+      <c r="F20" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="31" t="s">
         <v>0</v>
       </c>
       <c r="J20" s="61" t="s">
@@ -2819,20 +2808,20 @@
       <c r="C21" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="108"/>
+      <c r="D21" s="78"/>
       <c r="E21" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F21" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="H21" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="I21" s="109" t="s">
+      <c r="F21" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H21" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I21" s="31" t="s">
         <v>0</v>
       </c>
       <c r="J21" s="61" t="s">
@@ -2846,20 +2835,20 @@
       <c r="C22" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="108"/>
+      <c r="D22" s="78"/>
       <c r="E22" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F22" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="G22" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="H22" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="I22" s="109" t="s">
+      <c r="F22" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G22" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H22" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I22" s="31" t="s">
         <v>0</v>
       </c>
       <c r="J22" s="61" t="s">
@@ -2900,12 +2889,12 @@
       <c r="C24" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="105"/>
+      <c r="D24" s="71"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="105"/>
-      <c r="G24" s="105"/>
-      <c r="H24" s="105"/>
-      <c r="I24" s="105"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
       <c r="J24" s="58"/>
       <c r="K24" s="17"/>
     </row>
@@ -2913,20 +2902,20 @@
       <c r="C25" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="105"/>
+      <c r="D25" s="71"/>
       <c r="E25" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F25" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G25" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="H25" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I25" s="106" t="s">
+      <c r="F25" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H25" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I25" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J25" s="52" t="s">
@@ -2940,20 +2929,20 @@
       <c r="C26" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="105"/>
+      <c r="D26" s="71"/>
       <c r="E26" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G26" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="H26" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I26" s="106" t="s">
+      <c r="F26" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H26" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I26" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J26" s="52" t="s">
@@ -2967,20 +2956,20 @@
       <c r="C27" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="105"/>
+      <c r="D27" s="71"/>
       <c r="E27" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F27" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G27" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="H27" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I27" s="106" t="s">
+      <c r="F27" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J27" s="52" t="s">
@@ -2994,20 +2983,20 @@
       <c r="C28" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="105"/>
+      <c r="D28" s="71"/>
       <c r="E28" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F28" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="G28" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="H28" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="I28" s="106" t="s">
+      <c r="F28" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H28" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="I28" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J28" s="52" t="s">
@@ -3040,7 +3029,7 @@
       <c r="J29" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="K29" s="110" t="s">
+      <c r="K29" s="100" t="s">
         <v>0</v>
       </c>
     </row>

--- a/ABET/DocumentTracker_Assessment.xlsx
+++ b/ABET/DocumentTracker_Assessment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usarmywestpoint-my.sharepoint.com/personal/andrew_biaglow_westpoint_edu/Documents/Documents/GitHub/abiaglow.github.io/ABET/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16C30DEA-8C95-41EC-BD1F-75F6FB2F9DCC}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED1D00AC-1A4D-45D8-BA2F-C0D049E46261}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{188796DA-674F-42F3-8244-EB71C3832B77}"/>
+    <workbookView xWindow="22932" yWindow="-72" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{188796DA-674F-42F3-8244-EB71C3832B77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2462,8 +2462,8 @@
       <c r="J6" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="K6" s="66" t="s">
-        <v>52</v>
+      <c r="K6" s="70" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="3:11" x14ac:dyDescent="0.3">

--- a/ABET/DocumentTracker_Assessment.xlsx
+++ b/ABET/DocumentTracker_Assessment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usarmywestpoint-my.sharepoint.com/personal/andrew_biaglow_westpoint_edu/Documents/Documents/GitHub/abiaglow.github.io/ABET/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED1D00AC-1A4D-45D8-BA2F-C0D049E46261}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB7F7AE9-C6A0-4933-848E-B1C9B75C5BB9}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-72" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{188796DA-674F-42F3-8244-EB71C3832B77}"/>
   </bookViews>
@@ -2827,8 +2827,8 @@
       <c r="J21" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="K21" s="84" t="s">
-        <v>52</v>
+      <c r="K21" s="85" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="3:11" x14ac:dyDescent="0.3">

--- a/ABET/DocumentTracker_Assessment.xlsx
+++ b/ABET/DocumentTracker_Assessment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usarmywestpoint-my.sharepoint.com/personal/andrew_biaglow_westpoint_edu/Documents/Documents/GitHub/abiaglow.github.io/ABET/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB7F7AE9-C6A0-4933-848E-B1C9B75C5BB9}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{EFECDF9E-D228-4EC8-8531-E9F428053B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFC065BB-681E-408A-BD3B-14E27C1944F1}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-72" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{188796DA-674F-42F3-8244-EB71C3832B77}"/>
   </bookViews>
@@ -2543,8 +2543,8 @@
       <c r="J9" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="K9" s="67" t="s">
-        <v>53</v>
+      <c r="K9" s="77" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="3:11" x14ac:dyDescent="0.3">
